--- a/social media/C1/Reading2.xlsx
+++ b/social media/C1/Reading2.xlsx
@@ -28,10 +28,9 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="10"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -41,13 +40,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="004472C4"/>
-        <bgColor rgb="004472C4"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00EBF0FB"/>
-        <bgColor rgb="00EBF0FB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -71,7 +73,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -469,7 +471,7 @@
     <col width="45" customWidth="1" min="25" max="25"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>ID</t>
@@ -596,7 +598,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2">
       <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
@@ -617,12 +619,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>...of others, especially in unfamiliar cultural settings. In fact, it comes as no surprise that misunderstandings are (12) far more common in groups that share little in common. Seldom (13) do scientists encounter a behavioural pattern as...</t>
+          <t>...of others, especially in unfamiliar cultural settings. In fact, it comes as no surprise that misunderstandings are (12) far more common in groups that share little in common. Seldom...</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>...it comes as no surprise that misunderstandings are (12) far more common in groups that share little in common. Seldom (13) do scientists encounter a behavioural pattern as universal as mirroring, which appears across cultures and age groups...</t>
+          <t>...far more common in groups that share little in common. Seldom (13) do scientists encounter a behavioural pattern as universal as mirroring, which appears across cultures and age groups...</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -632,12 +634,12 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>...precisely. Not only does mirroring influence how we perceive others, but it can also determine how relationships end (15) up forming. Provided (16) any person in a group initiates a positive gesture, the rest often follow, reinforcing a...</t>
+          <t>...precisely. Not only does mirroring influence how we perceive others, but it can also determine how relationships end (15) up forming. Provided...</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>...mirroring influence how we perceive others, but it can also determine how relationships end (15) up forming. Provided (16) any person in a group initiates a positive gesture, the rest often follow, reinforcing a cycle of connection that...</t>
+          <t>...up forming. Provided (16) any person in a group initiates a positive gesture, the rest often follow, reinforcing a cycle of connection that...</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -682,7 +684,7 @@
       </c>
       <c r="R2" s="2" t="inlineStr">
         <is>
-          <t>Relative pronoun used to introduce a non-restrictive relative clause.</t>
+          <t>Relative pronoun used to introduce a non-restrictive relative clause. After a comma, only 'which' is acceptable (not 'that').</t>
         </is>
       </c>
       <c r="S2" s="2" t="inlineStr">
@@ -702,7 +704,7 @@
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>An auxiliary verb is required for negative inversion. When a sentence starts with a restrictive word like 'Seldom,' the ...</t>
+          <t>An auxiliary verb is required for negative inversion. When a sentence starts with a restrictive word like 'Seldom,' the subject and verb must flip.</t>
         </is>
       </c>
       <c r="W2" s="2" t="inlineStr">
@@ -717,27 +719,27 @@
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>Indefinite determiner used in conditional clauses meaning 'whichever' or 'if even one'.</t>
+          <t>Indefinite determiner used in conditional clauses meaning 'whichever' or 'if even one'. The fixed structure 'Provided any + noun' expresses a general condition.</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="60" customHeight="1">
+    <row r="3">
       <c r="A3" s="3" t="n">
         <v>2</v>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>...of a bird's wing or the water-repellent properties of a lotus leaf, engineers can develop technologies that are (9) more efficient than traditional models. One notable example is the Shinkansen bullet train in Japan, (10) redesigned...</t>
+          <t>...of a bird's wing or the water-repellent properties of a lotus leaf, engineers can develop technologies that are (9) more efficient than traditional models. One notable example is the Shinkansen bullet train in Japan,...</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>...that are (9) more efficient than traditional models. One notable example is the Shinkansen bullet train in Japan, (10) redesigned nose was modeled after the beak of a kingfisher to reduce noise pollution.   (11) only does this approach...</t>
+          <t>...more efficient than traditional models. One notable example is the Shinkansen bullet train in Japan, (10) redesigned nose was modeled after the beak of a kingfisher to reduce noise pollution.  ...</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>...bullet train in Japan, (10) redesigned nose was modeled after the beak of a kingfisher to reduce noise pollution.   (11) only does this approach lead to sustainable innovation, but it also highlights how much we have yet to learn from the...</t>
+          <t>...redesigned nose was modeled after the beak of a kingfisher to reduce noise pollution.   (11) only does this approach lead to sustainable innovation, but it also highlights how much we have yet to learn from the...</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -747,22 +749,22 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>...of sharkskin, for instance, hospitals might still be struggling to develop certain bacteria-resistant surfaces. (13) is widely recognized that nature has already solved many of the challenges we face today. However, (14) the vast...</t>
+          <t>...of sharkskin, for instance, hospitals might still be struggling to develop certain bacteria-resistant surfaces. (13) is widely recognized that nature has already solved many of the challenges we face today. However,...</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>...surfaces. (13) is widely recognized that nature has already solved many of the challenges we face today. However, (14) the vast potential of biomimicry, many industries have been slow to adopt these bio-inspired designs. This is often...</t>
+          <t>...is widely recognized that nature has already solved many of the challenges we face today. However, (14) the vast potential of biomimicry, many industries have been slow to adopt these bio-inspired designs. This is often...</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>...many industries have been slow to adopt these bio-inspired designs. This is often due to the high costs involved, (15) the long-term environmental benefits are clear. Ultimately, (16) is no doubt that as resources become scarcer, looking...</t>
+          <t>...many industries have been slow to adopt these bio-inspired designs. This is often due to the high costs involved, (15) the long-term environmental benefits are clear. Ultimately,...</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>...This is often due to the high costs involved, (15) the long-term environmental benefits are clear. Ultimately, (16) is no doubt that as resources become scarcer, looking to nature will become a necessity rather than a choice.</t>
+          <t>...the long-term environmental benefits are clear. Ultimately, (16) is no doubt that as resources become scarcer, looking to nature will become a necessity rather than a choice.</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -846,7 +848,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="60" customHeight="1">
+    <row r="4">
       <c r="A4" s="2" t="n">
         <v>3</v>
       </c>
@@ -857,32 +859,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>...minimalism is not merely about aesthetics, but about reclaiming time and mental space. Many proponents find themselves (10) a loss to explain why they ever felt the need to accumulate so much in the first place.   (11) it not for the...</t>
+          <t>...minimalism is not merely about aesthetics, but about reclaiming time and mental space. Many proponents find themselves (10) a loss to explain why they ever felt the need to accumulate so much in the first place.  ...</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>...find themselves (10) a loss to explain why they ever felt the need to accumulate so much in the first place.   (11) it not for the influence of social media, however, the trend might not have spread so rapidly. (12) only has it...</t>
+          <t>...a loss to explain why they ever felt the need to accumulate so much in the first place.   (11) it not for the influence of social media, however, the trend might not have spread so rapidly....</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>...the first place.   (11) it not for the influence of social media, however, the trend might not have spread so rapidly. (12) only has it influenced interior design, but it has also prompted a rethink of consumer habits. (13) the fact that...</t>
+          <t>...it not for the influence of social media, however, the trend might not have spread so rapidly. (12) only has it influenced interior design, but it has also prompted a rethink of consumer habits....</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>...spread so rapidly. (12) only has it influenced interior design, but it has also prompted a rethink of consumer habits. (13) the fact that buying less can be difficult in a consumerist society, many people are now prioritizing experiences over...</t>
+          <t>...only has it influenced interior design, but it has also prompted a rethink of consumer habits. (13) the fact that buying less can be difficult in a consumerist society, many people are now prioritizing experiences over...</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>...buying less can be difficult in a consumerist society, many people are now prioritizing experiences over objects. Such (14) the success of this movement that major brands are now marketing 'minimalist' products. (15) provided that this shift...</t>
+          <t>...buying less can be difficult in a consumerist society, many people are now prioritizing experiences over objects. Such (14) the success of this movement that major brands are now marketing 'minimalist' products....</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>...over objects. Such (14) the success of this movement that major brands are now marketing 'minimalist' products. (15) provided that this shift is genuine and not just another passing fad, it could lead to a more sustainable future for...</t>
+          <t>...the success of this movement that major brands are now marketing 'minimalist' products. (15) provided that this shift is genuine and not just another passing fad, it could lead to a more sustainable future for...</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -971,7 +973,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
+    <row r="5">
       <c r="A5" s="3" t="n">
         <v>4</v>
       </c>
@@ -982,32 +984,32 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>...emotions play in our decision-making. We like to believe we are rational beings, yet we often find ourselves (10) a loss when asked to justify our instinctive reactions.   (11) it not for our inherent cognitive biases, we might...</t>
+          <t>...emotions play in our decision-making. We like to believe we are rational beings, yet we often find ourselves (10) a loss when asked to justify our instinctive reactions.  ...</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>...we are rational beings, yet we often find ourselves (10) a loss when asked to justify our instinctive reactions.   (11) it not for our inherent cognitive biases, we might process data with clinical precision. (12) only do these biases...</t>
+          <t>...a loss when asked to justify our instinctive reactions.   (11) it not for our inherent cognitive biases, we might process data with clinical precision....</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>...instinctive reactions.   (11) it not for our inherent cognitive biases, we might process data with clinical precision. (12) only do these biases cloud our judgment, but they also reinforce existing prejudices. (13) the fact that education...</t>
+          <t>...it not for our inherent cognitive biases, we might process data with clinical precision. (12) only do these biases cloud our judgment, but they also reinforce existing prejudices....</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>...with clinical precision. (12) only do these biases cloud our judgment, but they also reinforce existing prejudices. (13) the fact that education systems are increasingly focusing on logic, the 'echo chamber' effect of the internet...</t>
+          <t>...only do these biases cloud our judgment, but they also reinforce existing prejudices. (13) the fact that education systems are increasingly focusing on logic, the 'echo chamber' effect of the internet...</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>...education systems are increasingly focusing on logic, the 'echo chamber' effect of the internet continues to grow. (14) is the power of social confirmation that many individuals prioritize being right over being accurate. (15) provided...</t>
+          <t>...education systems are increasingly focusing on logic, the 'echo chamber' effect of the internet continues to grow. (14) is the power of social confirmation that many individuals prioritize being right over being accurate....</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>...to grow. (14) is the power of social confirmation that many individuals prioritize being right over being accurate. (15) provided that we remain aware of these mental shortcuts can we hope to mitigate their effects. Ultimately, there is...</t>
+          <t>...is the power of social confirmation that many individuals prioritize being right over being accurate. (15) provided that we remain aware of these mental shortcuts can we hope to mitigate their effects. Ultimately, there is...</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
@@ -1096,48 +1098,48 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="60" customHeight="1">
+    <row r="6">
       <c r="A6" s="2" t="n">
         <v>5</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>...portion of the global population remains offline, a phenomenon known as the 'digital divide'. This gap exists (9) only between nations but also between urban and rural areas within the same country. (10) is the disparity that many...</t>
+          <t>...portion of the global population remains offline, a phenomenon known as the 'digital divide'. This gap exists (9) only between nations but also between urban and rural areas within the same country....</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>...divide'. This gap exists (9) only between nations but also between urban and rural areas within the same country. (10) is the disparity that many children in remote regions lack the resources for online education.   (11) should...</t>
+          <t>...only between nations but also between urban and rural areas within the same country. (10) is the disparity that many children in remote regions lack the resources for online education.  ...</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>...same country. (10) is the disparity that many children in remote regions lack the resources for online education.   (11) should governments ignore this issue, the economic consequences will be severe. (12) is no point in having advanced...</t>
+          <t>...is the disparity that many children in remote regions lack the resources for online education.   (11) should governments ignore this issue, the economic consequences will be severe....</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>...resources for online education.   (11) should governments ignore this issue, the economic consequences will be severe. (12) is no point in having advanced technology if half the world cannot use it. (13) whereas some countries have achieved...</t>
+          <t>...should governments ignore this issue, the economic consequences will be severe. (12) is no point in having advanced technology if half the world cannot use it....</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>...economic consequences will be severe. (12) is no point in having advanced technology if half the world cannot use it. (13) whereas some countries have achieved universal connectivity, others are struggling with outdated infrastructure. (14)...</t>
+          <t>...is no point in having advanced technology if half the world cannot use it. (13) whereas some countries have achieved universal connectivity, others are struggling with outdated infrastructure....</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>...(13) whereas some countries have achieved universal connectivity, others are struggling with outdated infrastructure. (14) least one major initiative has been launched to provide satellite internet to these regions. (15) any case, the...</t>
+          <t>...whereas some countries have achieved universal connectivity, others are struggling with outdated infrastructure. (14) least one major initiative has been launched to provide satellite internet to these regions....</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>...infrastructure. (14) least one major initiative has been launched to provide satellite internet to these regions. (15) any case, the success of such projects depends on local cooperation. This is a challenge (16) which there is no easy...</t>
+          <t>...least one major initiative has been launched to provide satellite internet to these regions. (15) any case, the success of such projects depends on local cooperation. This is a challenge...</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>...to these regions. (15) any case, the success of such projects depends on local cooperation. This is a challenge (16) which there is no easy solution, requiring both time and massive investment.</t>
+          <t>...any case, the success of such projects depends on local cooperation. This is a challenge (16) which there is no easy solution, requiring both time and massive investment.</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1221,7 +1223,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="60" customHeight="1">
+    <row r="7">
       <c r="A7" s="3" t="n">
         <v>6</v>
       </c>
@@ -1232,32 +1234,32 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>...repair themselves. In many cases, this involves the reintroduction of apex predators or 'keystone' species.   (10) it not for the return of wolves to Yellowstone Park, the entire river ecosystem might have remained degraded. Not (11)...</t>
+          <t>...repair themselves. In many cases, this involves the reintroduction of apex predators or 'keystone' species.   (10) it not for the return of wolves to Yellowstone Park, the entire river ecosystem might have remained degraded. Not...</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>...(10) it not for the return of wolves to Yellowstone Park, the entire river ecosystem might have remained degraded. Not (11) did the wolves control the deer population, but they also inadvertently changed the behavior of other animals,...</t>
+          <t>...it not for the return of wolves to Yellowstone Park, the entire river ecosystem might have remained degraded. Not (11) did the wolves control the deer population, but they also inadvertently changed the behavior of other animals,...</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>...the deer population, but they also inadvertently changed the behavior of other animals, allowing forests to recover. (12) comes as no surprise that such projects are gaining popularity worldwide. However, (13) the clear ecological benefits,...</t>
+          <t>...the deer population, but they also inadvertently changed the behavior of other animals, allowing forests to recover. (12) comes as no surprise that such projects are gaining popularity worldwide. However,...</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>...allowing forests to recover. (12) comes as no surprise that such projects are gaining popularity worldwide. However, (13) the clear ecological benefits, rewilding remains controversial among local farming communities. (14) far as these...</t>
+          <t>...comes as no surprise that such projects are gaining popularity worldwide. However, (13) the clear ecological benefits, rewilding remains controversial among local farming communities....</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>...However, (13) the clear ecological benefits, rewilding remains controversial among local farming communities. (14) far as these critics are concerned, the risk to livestock is simply too high. Nevertheless, (15) long as there is a...</t>
+          <t>...the clear ecological benefits, rewilding remains controversial among local farming communities. (14) far as these critics are concerned, the risk to livestock is simply too high. Nevertheless,...</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>...farming communities. (14) far as these critics are concerned, the risk to livestock is simply too high. Nevertheless, (15) long as there is a dialogue between scientists and locals, rewilding could become a cornerstone of future...</t>
+          <t>...far as these critics are concerned, the risk to livestock is simply too high. Nevertheless, (15) long as there is a dialogue between scientists and locals, rewilding could become a cornerstone of future...</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
@@ -1346,7 +1348,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="60" customHeight="1">
+    <row r="8">
       <c r="A8" s="2" t="n">
         <v>7</v>
       </c>
@@ -1357,37 +1359,37 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>...options is generally seen as a positive thing, too many can lead to anxiety and indecision. Psychology suggests that (10) more choices we have, the less satisfied we tend to be with our final decision.   (11) is widely thought that this...</t>
+          <t>...options is generally seen as a positive thing, too many can lead to anxiety and indecision. Psychology suggests that (10) more choices we have, the less satisfied we tend to be with our final decision.  ...</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>...Psychology suggests that (10) more choices we have, the less satisfied we tend to be with our final decision.   (11) is widely thought that this occurs because we become hyper-aware of the 'opportunity cost'—the benefits of the paths...</t>
+          <t>...more choices we have, the less satisfied we tend to be with our final decision.   (11) is widely thought that this occurs because we become hyper-aware of the 'opportunity cost'—the benefits of the paths...</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>...thought that this occurs because we become hyper-aware of the 'opportunity cost'—the benefits of the paths not taken. (12) should a person find themselves in such a position, they often end (13) feeling a sense of regret. (14) is the impact...</t>
+          <t>...thought that this occurs because we become hyper-aware of the 'opportunity cost'—the benefits of the paths not taken. (12) should a person find themselves in such a position, they often end...</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>...cost'—the benefits of the paths not taken. (12) should a person find themselves in such a position, they often end (13) feeling a sense of regret. (14) is the impact of this phenomenon that many marketing experts are now advising...</t>
+          <t>...should a person find themselves in such a position, they often end (13) feeling a sense of regret....</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>...not taken. (12) should a person find themselves in such a position, they often end (13) feeling a sense of regret. (14) is the impact of this phenomenon that many marketing experts are now advising companies to simplify their product...</t>
+          <t>...feeling a sense of regret. (14) is the impact of this phenomenon that many marketing experts are now advising companies to simplify their product...</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>...of this phenomenon that many marketing experts are now advising companies to simplify their product ranges. Seldom (15) a simpler approach failed to increase customer satisfaction. Ultimately, we must learn to be 'satisficers'—people (16)...</t>
+          <t>...of this phenomenon that many marketing experts are now advising companies to simplify their product ranges. Seldom (15) a simpler approach failed to increase customer satisfaction. Ultimately, we must learn to be 'satisficers'—people...</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>...(15) a simpler approach failed to increase customer satisfaction. Ultimately, we must learn to be 'satisficers'—people (16) are happy with a choice that is 'good enough' rather than perfect.</t>
+          <t>...a simpler approach failed to increase customer satisfaction. Ultimately, we must learn to be 'satisficers'—people (16) are happy with a choice that is 'good enough' rather than perfect.</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1471,43 +1473,43 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="60" customHeight="1">
+    <row r="9">
       <c r="A9" s="3" t="n">
         <v>8</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>...and celestial calendars (0) were far ahead of their time. However, by the 9th century, many of their great cities had (9) BEEN abandoned. (10) WHAT is still not fully understood is why such a sophisticated culture suddenly declined.   (11)...</t>
+          <t>...and celestial calendars (0) were far ahead of their time. However, by the 9th century, many of their great cities had (9) BEEN abandoned....</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>...(0) were far ahead of their time. However, by the 9th century, many of their great cities had (9) BEEN abandoned. (10) WHAT is still not fully understood is why such a sophisticated culture suddenly declined.   (11) AMONG the most likely...</t>
+          <t>...BEEN abandoned. (10) WHAT is still not fully understood is why such a sophisticated culture suddenly declined.  ...</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>...(9) BEEN abandoned. (10) WHAT is still not fully understood is why such a sophisticated culture suddenly declined.   (11) AMONG the most likely theories point to a combination of prolonged drought and over-farming. (12) SHOULD this be the...</t>
+          <t>...WHAT is still not fully understood is why such a sophisticated culture suddenly declined.   (11) AMONG the most likely theories point to a combination of prolonged drought and over-farming....</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>...suddenly declined.   (11) AMONG the most likely theories point to a combination of prolonged drought and over-farming. (12) SHOULD this be the case, it would serve as a stark warning about environmental mismanagement. (13) AS far as...</t>
+          <t>...AMONG the most likely theories point to a combination of prolonged drought and over-farming. (12) SHOULD this be the case, it would serve as a stark warning about environmental mismanagement....</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>...and over-farming. (12) SHOULD this be the case, it would serve as a stark warning about environmental mismanagement. (13) AS far as archaeologists can tell, there was no single catastrophic event, but rather a slow disintegration. (14) NOT...</t>
+          <t>...SHOULD this be the case, it would serve as a stark warning about environmental mismanagement. (13) AS far as archaeologists can tell, there was no single catastrophic event, but rather a slow disintegration....</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>...(13) AS far as archaeologists can tell, there was no single catastrophic event, but rather a slow disintegration. (14) NOT only did the population dwindle, but the social order itself seems to have collapsed. (15) ONLY provided that new...</t>
+          <t>...AS far as archaeologists can tell, there was no single catastrophic event, but rather a slow disintegration. (14) NOT only did the population dwindle, but the social order itself seems to have collapsed....</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>...a slow disintegration. (14) NOT only did the population dwindle, but the social order itself seems to have collapsed. (15) ONLY provided that new LIDAR technology continues to uncover hidden structures in the jungle, we may soon have more...</t>
+          <t>...NOT only did the population dwindle, but the social order itself seems to have collapsed. (15) ONLY provided that new LIDAR technology continues to uncover hidden structures in the jungle, we may soon have more...</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
@@ -1596,7 +1598,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="60" customHeight="1">
+    <row r="10">
       <c r="A10" s="2" t="n">
         <v>9</v>
       </c>
@@ -1612,32 +1614,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>...WERE it not for this nocturnal activity, our ability to process memories and emotions would be severely impaired. Not (11) ONLY does sleep help consolidate what we have learned during the day, but it also flushes out toxins. (12) IT is...</t>
+          <t>...WERE it not for this nocturnal activity, our ability to process memories and emotions would be severely impaired. Not (11) ONLY does sleep help consolidate what we have learned during the day, but it also flushes out toxins....</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>...Not (11) ONLY does sleep help consolidate what we have learned during the day, but it also flushes out toxins. (12) IT is widely believed that chronic sleep deprivation can lead to serious health issues. However, (13) DESPITE the...</t>
+          <t>...ONLY does sleep help consolidate what we have learned during the day, but it also flushes out toxins. (12) IT is widely believed that chronic sleep deprivation can lead to serious health issues. However,...</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>...out toxins. (12) IT is widely believed that chronic sleep deprivation can lead to serious health issues. However, (13) DESPITE the overwhelming evidence of its importance, many people continue to sacrifice sleep for work or...</t>
+          <t>...IT is widely believed that chronic sleep deprivation can lead to serious health issues. However, (13) DESPITE the overwhelming evidence of its importance, many people continue to sacrifice sleep for work or...</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>...to sacrifice sleep for work or entertainment. The long-term cognitive effects of chronic sleep deprivation are (14) BEYOND doubt serious and potentially irreversible. (15) AS far as current research is concerned, seven to nine hours...</t>
+          <t>...to sacrifice sleep for work or entertainment. The long-term cognitive effects of chronic sleep deprivation are (14) BEYOND doubt serious and potentially irreversible....</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>...long-term cognitive effects of chronic sleep deprivation are (14) BEYOND doubt serious and potentially irreversible. (15) AS far as current research is concerned, seven to nine hours remains the 'gold standard'. Ultimately, there is (16) NO...</t>
+          <t>...BEYOND doubt serious and potentially irreversible. (15) AS far as current research is concerned, seven to nine hours remains the 'gold standard'. Ultimately, there is...</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>...(15) AS far as current research is concerned, seven to nine hours remains the 'gold standard'. Ultimately, there is (16) NO doubt that prioritizing rest is essential for a productive life.</t>
+          <t>...AS far as current research is concerned, seven to nine hours remains the 'gold standard'. Ultimately, there is (16) NO doubt that prioritizing rest is essential for a productive life.</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1721,48 +1723,48 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="60" customHeight="1">
+    <row r="11">
       <c r="A11" s="3" t="n">
         <v>10</v>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>...(0) human history. Early cities emerged in Mesopotamia, where the fertile land allowed for agricultural surpluses. (9) IT was this surplus that enabled a division of labor, leading to the rise of specialized craftsmen and priests.   (10)...</t>
+          <t>...(0) human history. Early cities emerged in Mesopotamia, where the fertile land allowed for agricultural surpluses. (9) IT was this surplus that enabled a division of labor, leading to the rise of specialized craftsmen and priests.  ...</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>...(9) IT was this surplus that enabled a division of labor, leading to the rise of specialized craftsmen and priests.   (10) HAD it not been for the development of irrigation systems, these early civilizations might never have flourished. (11)...</t>
+          <t>...IT was this surplus that enabled a division of labor, leading to the rise of specialized craftsmen and priests.   (10) HAD it not been for the development of irrigation systems, these early civilizations might never have flourished....</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>...(10) HAD it not been for the development of irrigation systems, these early civilizations might never have flourished. (11) WHAT is often argued is that the density of city life accelerated technological progress. However, (12) SUCH is the...</t>
+          <t>...HAD it not been for the development of irrigation systems, these early civilizations might never have flourished. (11) WHAT is often argued is that the density of city life accelerated technological progress. However,...</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>...flourished. (11) WHAT is often argued is that the density of city life accelerated technological progress. However, (12) SUCH is the complexity of urban planning that even today, modern architects struggle to balance growth with...</t>
+          <t>...WHAT is often argued is that the density of city life accelerated technological progress. However, (12) SUCH is the complexity of urban planning that even today, modern architects struggle to balance growth with...</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>...is the complexity of urban planning that even today, modern architects struggle to balance growth with sustainability. (13) EVEN though ancient cities lacked modern plumbing, their social structures were incredibly sophisticated. (14) AT...</t>
+          <t>...is the complexity of urban planning that even today, modern architects struggle to balance growth with sustainability. (13) EVEN though ancient cities lacked modern plumbing, their social structures were incredibly sophisticated....</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>...(13) EVEN though ancient cities lacked modern plumbing, their social structures were incredibly sophisticated. (14) AT least one major theory suggests that climate change was responsible for the abandonment of some early settlements....</t>
+          <t>...EVEN though ancient cities lacked modern plumbing, their social structures were incredibly sophisticated. (14) AT least one major theory suggests that climate change was responsible for the abandonment of some early settlements....</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>...one major theory suggests that climate change was responsible for the abandonment of some early settlements. Seldom (15) HAS humanity faced such a challenge as managing the mega-cities of the 21st century. (16) ONLY provided that we learn...</t>
+          <t>...one major theory suggests that climate change was responsible for the abandonment of some early settlements. Seldom (15) HAS humanity faced such a challenge as managing the mega-cities of the 21st century....</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>...early settlements. Seldom (15) HAS humanity faced such a challenge as managing the mega-cities of the 21st century. (16) ONLY provided that we learn from the past, we can build more resilient urban futures.</t>
+          <t>...HAS humanity faced such a challenge as managing the mega-cities of the 21st century. (16) ONLY provided that we learn from the past, we can build more resilient urban futures.</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1846,48 +1848,48 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="60" customHeight="1">
+    <row r="12">
       <c r="A12" s="2" t="n">
         <v>11</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>...(0) human history. Early cities emerged in Mesopotamia, where the fertile land allowed for agricultural surpluses. (9) IT was this surplus that enabled a division of labor, leading to the rise of specialized craftsmen and priests.   (10)...</t>
+          <t>...(0) human history. Early cities emerged in Mesopotamia, where the fertile land allowed for agricultural surpluses. (9) IT was this surplus that enabled a division of labor, leading to the rise of specialized craftsmen and priests.  ...</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>...(9) IT was this surplus that enabled a division of labor, leading to the rise of specialized craftsmen and priests.   (10) HAD it not been for the development of irrigation systems, these early civilizations might never have flourished. (11)...</t>
+          <t>...IT was this surplus that enabled a division of labor, leading to the rise of specialized craftsmen and priests.   (10) HAD it not been for the development of irrigation systems, these early civilizations might never have flourished....</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>...(10) HAD it not been for the development of irrigation systems, these early civilizations might never have flourished. (11) WHAT is often argued is that the density of city life accelerated technological progress. However, (12) SUCH is the...</t>
+          <t>...HAD it not been for the development of irrigation systems, these early civilizations might never have flourished. (11) WHAT is often argued is that the density of city life accelerated technological progress. However,...</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>...flourished. (11) WHAT is often argued is that the density of city life accelerated technological progress. However, (12) SUCH is the complexity of urban planning that even today, modern architects struggle to balance growth with...</t>
+          <t>...WHAT is often argued is that the density of city life accelerated technological progress. However, (12) SUCH is the complexity of urban planning that even today, modern architects struggle to balance growth with...</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>...is the complexity of urban planning that even today, modern architects struggle to balance growth with sustainability. (13) EVEN though ancient cities lacked modern plumbing, their social structures were incredibly sophisticated. (14) AT...</t>
+          <t>...is the complexity of urban planning that even today, modern architects struggle to balance growth with sustainability. (13) EVEN though ancient cities lacked modern plumbing, their social structures were incredibly sophisticated....</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>...(13) EVEN though ancient cities lacked modern plumbing, their social structures were incredibly sophisticated. (14) AT least one major theory suggests that climate change was responsible for the abandonment of some early settlements....</t>
+          <t>...EVEN though ancient cities lacked modern plumbing, their social structures were incredibly sophisticated. (14) AT least one major theory suggests that climate change was responsible for the abandonment of some early settlements....</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>...one major theory suggests that climate change was responsible for the abandonment of some early settlements. Seldom (15) HAS humanity faced such a challenge as managing the mega-cities of the 21st century. (16) ONLY provided that we learn...</t>
+          <t>...one major theory suggests that climate change was responsible for the abandonment of some early settlements. Seldom (15) HAS humanity faced such a challenge as managing the mega-cities of the 21st century....</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>...early settlements. Seldom (15) HAS humanity faced such a challenge as managing the mega-cities of the 21st century. (16) ONLY provided that we learn from the past, we can build more resilient urban futures.</t>
+          <t>...HAS humanity faced such a challenge as managing the mega-cities of the 21st century. (16) ONLY provided that we learn from the past, we can build more resilient urban futures.</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1971,28 +1973,28 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="60" customHeight="1">
+    <row r="13">
       <c r="A13" s="3" t="n">
         <v>12</v>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>...prevalence of short-term contracts and freelance work. In this model, individuals often work for multiple employers (9) RATHER than being committed to a single company. (10) HOWEVER simple this flexibility may seem, it presents...</t>
+          <t>...prevalence of short-term contracts and freelance work. In this model, individuals often work for multiple employers (9) RATHER than being committed to a single company....</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>...In this model, individuals often work for multiple employers (9) RATHER than being committed to a single company. (10) HOWEVER simple this flexibility may seem, it presents significant challenges regarding workers' rights and job...</t>
+          <t>...RATHER than being committed to a single company. (10) HOWEVER simple this flexibility may seem, it presents significant challenges regarding workers' rights and job...</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>...simple this flexibility may seem, it presents significant challenges regarding workers' rights and job security.   (11) should an economic downturn occur, gig workers are often the first to lose their income. (12) IT is widely recognized...</t>
+          <t>...simple this flexibility may seem, it presents significant challenges regarding workers' rights and job security.   (11) should an economic downturn occur, gig workers are often the first to lose their income....</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>...and job security.   (11) should an economic downturn occur, gig workers are often the first to lose their income. (12) IT is widely recognized that the lack of traditional benefits, such as health insurance or paid leave, is a major...</t>
+          <t>...should an economic downturn occur, gig workers are often the first to lose their income. (12) IT is widely recognized that the lack of traditional benefits, such as health insurance or paid leave, is a major...</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
@@ -2007,12 +2009,12 @@
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>...only does the gig economy provide extra income for many, but it also allows for a better work-life balance for some. (15) ONLY provided that new regulations are introduced, this sector will continue to expand. Ultimately, there is (16) NO...</t>
+          <t>...only does the gig economy provide extra income for many, but it also allows for a better work-life balance for some. (15) ONLY provided that new regulations are introduced, this sector will continue to expand. Ultimately, there is...</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>...(15) ONLY provided that new regulations are introduced, this sector will continue to expand. Ultimately, there is (16) NO doubt that the way we define 'work' is changing forever.</t>
+          <t>...ONLY provided that new regulations are introduced, this sector will continue to expand. Ultimately, there is (16) NO doubt that the way we define 'work' is changing forever.</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -2062,7 +2064,7 @@
       </c>
       <c r="S13" s="3" t="inlineStr">
         <is>
-          <t>Used to introduce a concessive adverbial clause meaning 'no matter how'.</t>
+          <t>Used to introduce a concessive adverbial clause meaning 'no matter how'. 'However + adjective + subject + verb' expresses contrast or concession.</t>
         </is>
       </c>
       <c r="T13" s="3" t="inlineStr">
@@ -2096,48 +2098,48 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="60" customHeight="1">
+    <row r="14">
       <c r="A14" s="2" t="n">
         <v>13</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>...This hidden web acts as a biological communication system, allowing trees to share nutrients and even warn one (9) ANOTHER of incoming pests. (10) WERE it not for this 'Wood Wide Web', many forests would be far less resilient to...</t>
+          <t>...This hidden web acts as a biological communication system, allowing trees to share nutrients and even warn one (9) ANOTHER of incoming pests....</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>...a biological communication system, allowing trees to share nutrients and even warn one (9) ANOTHER of incoming pests. (10) WERE it not for this 'Wood Wide Web', many forests would be far less resilient to environmental stress.   (11) IT is...</t>
+          <t>...ANOTHER of incoming pests. (10) WERE it not for this 'Wood Wide Web', many forests would be far less resilient to environmental stress.  ...</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>...pests. (10) WERE it not for this 'Wood Wide Web', many forests would be far less resilient to environmental stress.   (11) IT is often observed that older trees, or 'mother trees', use this network to support younger saplings. Not (12) ONLY...</t>
+          <t>...WERE it not for this 'Wood Wide Web', many forests would be far less resilient to environmental stress.   (11) IT is often observed that older trees, or 'mother trees', use this network to support younger saplings. Not...</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>...  (11) IT is often observed that older trees, or 'mother trees', use this network to support younger saplings. Not (12) ONLY does this interaction increase the survival rate of the forest, but it also maintains genetic diversity. (13)...</t>
+          <t>...IT is often observed that older trees, or 'mother trees', use this network to support younger saplings. Not (12) ONLY does this interaction increase the survival rate of the forest, but it also maintains genetic diversity....</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>...Not (12) ONLY does this interaction increase the survival rate of the forest, but it also maintains genetic diversity. (13) DESPITE the importance of this system, it remains largely invisible to the casual observer. (14) AS far as scientists...</t>
+          <t>...ONLY does this interaction increase the survival rate of the forest, but it also maintains genetic diversity. (13) DESPITE the importance of this system, it remains largely invisible to the casual observer....</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>...genetic diversity. (13) DESPITE the importance of this system, it remains largely invisible to the casual observer. (14) AS far as scientists can tell, these fungal relationships have existed for millions of years. However, (15) SUCH is...</t>
+          <t>...DESPITE the importance of this system, it remains largely invisible to the casual observer. (14) AS far as scientists can tell, these fungal relationships have existed for millions of years. However,...</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>...observer. (14) AS far as scientists can tell, these fungal relationships have existed for millions of years. However, (15) SUCH is the fragility of this balance that modern deforestation can destroy it in an instant. (16) SO long as we...</t>
+          <t>...AS far as scientists can tell, these fungal relationships have existed for millions of years. However, (15) SUCH is the fragility of this balance that modern deforestation can destroy it in an instant....</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>...of years. However, (15) SUCH is the fragility of this balance that modern deforestation can destroy it in an instant. (16) SO long as we protect our soil, this ancient network will continue to sustain life on Earth for future generations.</t>
+          <t>...SUCH is the fragility of this balance that modern deforestation can destroy it in an instant. (16) SO long as we protect our soil, this ancient network will continue to sustain life on Earth for future generations.</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -2221,43 +2223,43 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="60" customHeight="1">
+    <row r="15">
       <c r="A15" s="3" t="n">
         <v>14</v>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>...of the Dutch Golden Age. However, for centuries, his name was largely forgotten, and his works were often attributed (9) other artists. (10) is still a mystery is how a painter of such immense talent produced so few recorded works—only...</t>
+          <t>...of the Dutch Golden Age. However, for centuries, his name was largely forgotten, and his works were often attributed (9) other artists....</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>...Age. However, for centuries, his name was largely forgotten, and his works were often attributed (9) other artists. (10) is still a mystery is how a painter of such immense talent produced so few recorded works—only about thirty-five are...</t>
+          <t>...other artists. (10) is still a mystery is how a painter of such immense talent produced so few recorded works—only about thirty-five are...</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>...is how a painter of such immense talent produced so few recorded works—only about thirty-five are known to exist.   (11) it not for the rediscovery of his work by critics in the 19th century, Vermeer might still be an obscure figure. (12)...</t>
+          <t>...is how a painter of such immense talent produced so few recorded works—only about thirty-five are known to exist.   (11) it not for the rediscovery of his work by critics in the 19th century, Vermeer might still be an obscure figure....</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>... (11) it not for the rediscovery of his work by critics in the 19th century, Vermeer might still be an obscure figure. (12) only is his use of light unparalleled, but his mastery of color continues to captivate modern audiences. (13) is...</t>
+          <t>...it not for the rediscovery of his work by critics in the 19th century, Vermeer might still be an obscure figure. (12) only is his use of light unparalleled, but his mastery of color continues to captivate modern audiences....</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>...figure. (12) only is his use of light unparalleled, but his mastery of color continues to captivate modern audiences. (13) is widely suspected that he used a 'camera obscura' to achieve his signature precision. (14) if this were true, it...</t>
+          <t>...only is his use of light unparalleled, but his mastery of color continues to captivate modern audiences. (13) is widely suspected that he used a 'camera obscura' to achieve his signature precision....</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>...modern audiences. (13) is widely suspected that he used a 'camera obscura' to achieve his signature precision. (14) if this were true, it would not diminish his artistic genius. (15) whereas many of his contemporaries painted grand...</t>
+          <t>...is widely suspected that he used a 'camera obscura' to achieve his signature precision. (14) if this were true, it would not diminish his artistic genius....</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>...obscura' to achieve his signature precision. (14) if this were true, it would not diminish his artistic genius. (15) whereas many of his contemporaries painted grand historical scenes, Vermeer focused on quiet, domestic moments. Today,...</t>
+          <t>...if this were true, it would not diminish his artistic genius. (15) whereas many of his contemporaries painted grand historical scenes, Vermeer focused on quiet, domestic moments. Today,...</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
@@ -2346,18 +2348,18 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="60" customHeight="1">
+    <row r="16">
       <c r="A16" s="2" t="n">
         <v>15</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>...to bring the impossible (0) life. Early pioneers like Georges Méliès used clever camera tricks to create illusions. (9) HOWEVER simple these techniques might seem to a modern audience, they were groundbreaking at the time.   (10) should a...</t>
+          <t>...to bring the impossible (0) life. Early pioneers like Georges Méliès used clever camera tricks to create illusions. (9) HOWEVER simple these techniques might seem to a modern audience, they were groundbreaking at the time.  ...</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>...(9) HOWEVER simple these techniques might seem to a modern audience, they were groundbreaking at the time.   (10) should a viewer watch these early films today, they would still find a certain charm in their hand-crafted nature....</t>
+          <t>...HOWEVER simple these techniques might seem to a modern audience, they were groundbreaking at the time.   (10) should a viewer watch these early films today, they would still find a certain charm in their hand-crafted nature....</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -2367,12 +2369,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>...IT is often argued that the transition to Computer Generated Imagery (CGI) has robbed cinema of its tactile quality. (12) AS far as some purists are concerned, practical effects are always superior to digital ones. (13) SUCH is the demand...</t>
+          <t>...IT is often argued that the transition to Computer Generated Imagery (CGI) has robbed cinema of its tactile quality. (12) AS far as some purists are concerned, practical effects are always superior to digital ones....</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>...its tactile quality. (12) AS far as some purists are concerned, practical effects are always superior to digital ones. (13) SUCH is the demand for realism in blockbuster movies that studios now spend hundreds of millions on visual effects....</t>
+          <t>...AS far as some purists are concerned, practical effects are always superior to digital ones. (13) SUCH is the demand for realism in blockbuster movies that studios now spend hundreds of millions on visual effects....</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2432,7 +2434,7 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>Used to introduce a concessive adverbial clause. 'However + adjective + subject + verb' is a formal structure expressing...</t>
+          <t>Used to introduce a concessive adverbial clause. 'However + adjective + subject + verb' is a formal structure expressing contrast.</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
@@ -2471,48 +2473,48 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="60" customHeight="1">
+    <row r="17">
       <c r="A17" s="3" t="n">
         <v>16</v>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>...the ability to produce their own light, (0) a phenomenon known as bioluminescence. This biological light is produced (9) by a chemical reaction between a light-emitting molecule and an enzyme. (10) Although it may seem like a rare...</t>
+          <t>...the ability to produce their own light, (0) a phenomenon known as bioluminescence. This biological light is produced (9) by a chemical reaction between a light-emitting molecule and an enzyme....</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>...This biological light is produced (9) by a chemical reaction between a light-emitting molecule and an enzyme. (10) Although it may seem like a rare occurrence to us, it is actually quite common in the deep sea. It serves a variety of...</t>
+          <t>...by a chemical reaction between a light-emitting molecule and an enzyme. (10) Although it may seem like a rare occurrence to us, it is actually quite common in the deep sea. It serves a variety of...</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>...may seem like a rare occurrence to us, it is actually quite common in the deep sea. It serves a variety of purposes, (11) such as attracting prey, finding mates, or deterring predators. Some fish use light to blend (12) in with the faint...</t>
+          <t>...may seem like a rare occurrence to us, it is actually quite common in the deep sea. It serves a variety of purposes, (11) such as attracting prey, finding mates, or deterring predators. Some fish use light to blend...</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>...variety of purposes, (11) such as attracting prey, finding mates, or deterring predators. Some fish use light to blend (12) in with the faint glow from the surface, making them nearly invisible to hunters below. (13) Not only is this light...</t>
+          <t>...such as attracting prey, finding mates, or deterring predators. Some fish use light to blend (12) in with the faint glow from the surface, making them nearly invisible to hunters below....</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>...fish use light to blend (12) in with the faint glow from the surface, making them nearly invisible to hunters below. (13) Not only is this light used for survival, but it also allows for complex communication in the dark. (14) Despite the...</t>
+          <t>...in with the faint glow from the surface, making them nearly invisible to hunters below. (13) Not only is this light used for survival, but it also allows for complex communication in the dark....</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>...below. (13) Not only is this light used for survival, but it also allows for complex communication in the dark. (14) Despite the immense pressure and freezing temperatures, these organisms thrive in an environment (15) that would be...</t>
+          <t>...Not only is this light used for survival, but it also allows for complex communication in the dark. (14) Despite the immense pressure and freezing temperatures, these organisms thrive in an environment...</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>...in the dark. (14) Despite the immense pressure and freezing temperatures, these organisms thrive in an environment (15) that would be fatal to most life forms. Scientists are only just beginning to understand the full extent of (16) how...</t>
+          <t>...Despite the immense pressure and freezing temperatures, these organisms thrive in an environment (15) that would be fatal to most life forms. Scientists are only just beginning to understand the full extent of...</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>...(15) that would be fatal to most life forms. Scientists are only just beginning to understand the full extent of (16) how bioluminescence impacts the marine ecosystem. This mysterious world continues to provide us with new insights into...</t>
+          <t>...that would be fatal to most life forms. Scientists are only just beginning to understand the full extent of (16) how bioluminescence impacts the marine ecosystem. This mysterious world continues to provide us with new insights into...</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -2596,33 +2598,33 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="60" customHeight="1">
+    <row r="18">
       <c r="A18" s="2" t="n">
         <v>17</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>...provided the key (0) to unlocking the mysteries of ancient Egyptian hieroglyphs. For centuries, this complex script (9) had remained undecipherable, its meaning lost to time. The stone features a decree issued in 196 BC (10) on behalf of...</t>
+          <t>...provided the key (0) to unlocking the mysteries of ancient Egyptian hieroglyphs. For centuries, this complex script (9) had remained undecipherable, its meaning lost to time. The stone features a decree issued in 196 BC...</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>...complex script (9) had remained undecipherable, its meaning lost to time. The stone features a decree issued in 196 BC (10) on behalf of King Ptolemy V. Crucially, the text appears in three different scripts: hieroglyphic, Demotic, and...</t>
+          <t>...had remained undecipherable, its meaning lost to time. The stone features a decree issued in 196 BC (10) on behalf of King Ptolemy V. Crucially, the text appears in three different scripts: hieroglyphic, Demotic, and...</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>...of King Ptolemy V. Crucially, the text appears in three different scripts: hieroglyphic, Demotic, and Ancient Greek. (11) Since the Greek text was well understood, it served (12) as a vital translation tool for researchers. (13) Not until...</t>
+          <t>...of King Ptolemy V. Crucially, the text appears in three different scripts: hieroglyphic, Demotic, and Ancient Greek. (11) Since the Greek text was well understood, it served...</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>...different scripts: hieroglyphic, Demotic, and Ancient Greek. (11) Since the Greek text was well understood, it served (12) as a vital translation tool for researchers. (13) Not until the work of Jean-François Champollion in the 1820s was the...</t>
+          <t>...Since the Greek text was well understood, it served (12) as a vital translation tool for researchers....</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>...Greek. (11) Since the Greek text was well understood, it served (12) as a vital translation tool for researchers. (13) Not until the work of Jean-François Champollion in the 1820s was the code finally broken. Champollion realized that...</t>
+          <t>...as a vital translation tool for researchers. (13) Not until the work of Jean-François Champollion in the 1820s was the code finally broken. Champollion realized that...</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2721,7 +2723,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="60" customHeight="1">
+    <row r="19">
       <c r="A19" s="3" t="n">
         <v>18</v>
       </c>
@@ -2737,32 +2739,32 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>...you are painting a masterpiece or solving a complex puzzle, being in flow means your skills are perfectly balanced (11) against the challenge at hand. If the task is too easy, boredom sets (12) in; if it is too difficult, anxiety arises....</t>
+          <t>...you are painting a masterpiece or solving a complex puzzle, being in flow means your skills are perfectly balanced (11) against the challenge at hand. If the task is too easy, boredom sets...</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>...means your skills are perfectly balanced (11) against the challenge at hand. If the task is too easy, boredom sets (12) in; if it is too difficult, anxiety arises. (13) Not until this equilibrium is reached can an individual experience...</t>
+          <t>...against the challenge at hand. If the task is too easy, boredom sets (12) in; if it is too difficult, anxiety arises....</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>...against the challenge at hand. If the task is too easy, boredom sets (12) in; if it is too difficult, anxiety arises. (13) Not until this equilibrium is reached can an individual experience the sense of effortless control that defines the...</t>
+          <t>...in; if it is too difficult, anxiety arises. (13) Not until this equilibrium is reached can an individual experience the sense of effortless control that defines the...</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>...can an individual experience the sense of effortless control that defines the flow state. Research suggests that flow (14) not only improves performance but also contributes significantly to overall well-being. (15) Despite its benefits,...</t>
+          <t>...can an individual experience the sense of effortless control that defines the flow state. Research suggests that flow (14) not only improves performance but also contributes significantly to overall well-being....</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>...suggests that flow (14) not only improves performance but also contributes significantly to overall well-being. (15) Despite its benefits, achieving flow requires a clear goal and immediate feedback. (16) Such is the power of this...</t>
+          <t>...not only improves performance but also contributes significantly to overall well-being. (15) Despite its benefits, achieving flow requires a clear goal and immediate feedback....</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>...to overall well-being. (15) Despite its benefits, achieving flow requires a clear goal and immediate feedback. (16) Such is the power of this phenomenon that it can transform mundane tasks into deeply rewarding experiences. Many...</t>
+          <t>...Despite its benefits, achieving flow requires a clear goal and immediate feedback. (16) Such is the power of this phenomenon that it can transform mundane tasks into deeply rewarding experiences. Many...</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -2846,38 +2848,38 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="60" customHeight="1">
+    <row r="20">
       <c r="A20" s="2" t="n">
         <v>19</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>...remains one of history’s greatest losses. Established during the third century BC, the library aimed to house (9) every single manuscript ever written. Scholars from across the Mediterranean flocked to the city (10) to study its...</t>
+          <t>...remains one of history’s greatest losses. Established during the third century BC, the library aimed to house (9) every single manuscript ever written. Scholars from across the Mediterranean flocked to the city...</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>...aimed to house (9) every single manuscript ever written. Scholars from across the Mediterranean flocked to the city (10) to study its vast and diverse collection of intellectual works. However, (11) despite its prestige, the library’s...</t>
+          <t>...every single manuscript ever written. Scholars from across the Mediterranean flocked to the city (10) to study its vast and diverse collection of intellectual works. However,...</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>...the Mediterranean flocked to the city (10) to study its vast and diverse collection of intellectual works. However, (11) despite its prestige, the library’s eventual demise is shrouded in mystery. Some historians argue that it was burned...</t>
+          <t>...to study its vast and diverse collection of intellectual works. However, (11) despite its prestige, the library’s eventual demise is shrouded in mystery. Some historians argue that it was burned...</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>...despite its prestige, the library’s eventual demise is shrouded in mystery. Some historians argue that it was burned (12) down during Julius Caesar’s siege, (13) while others suggest a gradual decline caused by lack of funding. (14) Not...</t>
+          <t>...despite its prestige, the library’s eventual demise is shrouded in mystery. Some historians argue that it was burned (12) down during Julius Caesar’s siege,...</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>...demise is shrouded in mystery. Some historians argue that it was burned (12) down during Julius Caesar’s siege, (13) while others suggest a gradual decline caused by lack of funding. (14) Not until centuries later did researchers...</t>
+          <t>...down during Julius Caesar’s siege, (13) while others suggest a gradual decline caused by lack of funding....</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>...burned (12) down during Julius Caesar’s siege, (13) while others suggest a gradual decline caused by lack of funding. (14) Not until centuries later did researchers realize that much of the gathered knowledge had actually been preserved...</t>
+          <t>...while others suggest a gradual decline caused by lack of funding. (14) Not until centuries later did researchers realize that much of the gathered knowledge had actually been preserved...</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -2971,43 +2973,43 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="60" customHeight="1">
+    <row r="21">
       <c r="A21" s="3" t="n">
         <v>20</v>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>...of the Earth’s lithosphere, (0) which is composed of several massive plates. These plates are constantly moving, (9) although the speed at which they drift is roughly equivalent to the rate (10) at which human fingernails grow. (11)...</t>
+          <t>...of the Earth’s lithosphere, (0) which is composed of several massive plates. These plates are constantly moving, (9) although the speed at which they drift is roughly equivalent to the rate...</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>...These plates are constantly moving, (9) although the speed at which they drift is roughly equivalent to the rate (10) at which human fingernails grow. (11) Provided that these movements continue, the configuration of our continents will...</t>
+          <t>...although the speed at which they drift is roughly equivalent to the rate (10) at which human fingernails grow....</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>...(9) although the speed at which they drift is roughly equivalent to the rate (10) at which human fingernails grow. (11) Provided that these movements continue, the configuration of our continents will look entirely different in millions...</t>
+          <t>...at which human fingernails grow. (11) Provided that these movements continue, the configuration of our continents will look entirely different in millions...</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>...configuration of our continents will look entirely different in millions of years. This dynamic process is responsible (12) for the creation of mountain ranges, volcanic activity, and earthquakes. (13) Not only does tectonics shape the...</t>
+          <t>...configuration of our continents will look entirely different in millions of years. This dynamic process is responsible (12) for the creation of mountain ranges, volcanic activity, and earthquakes....</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>...This dynamic process is responsible (12) for the creation of mountain ranges, volcanic activity, and earthquakes. (13) Not only does tectonics shape the physical landscape, but it also influences the planet’s climate over geological...</t>
+          <t>...for the creation of mountain ranges, volcanic activity, and earthquakes. (13) Not only does tectonics shape the physical landscape, but it also influences the planet’s climate over geological...</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>...landscape, but it also influences the planet’s climate over geological timescales. Scientists monitor these shifts (14) by means of satellite technology and seismic sensors, which provide precise data on crustal deformation. (15) Since...</t>
+          <t>...landscape, but it also influences the planet’s climate over geological timescales. Scientists monitor these shifts (14) by means of satellite technology and seismic sensors, which provide precise data on crustal deformation....</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>...shifts (14) by means of satellite technology and seismic sensors, which provide precise data on crustal deformation. (15) Since the theory was first proposed, it has revolutionized our understanding of the Earth’s internal heat and its...</t>
+          <t>...by means of satellite technology and seismic sensors, which provide precise data on crustal deformation. (15) Since the theory was first proposed, it has revolutionized our understanding of the Earth’s internal heat and its...</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
@@ -3096,38 +3098,38 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="60" customHeight="1">
+    <row r="22">
       <c r="A22" s="2" t="n">
         <v>21</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>...(0) where a patient experiences a real improvement in their condition after receiving a dummy treatment. This occurs (9) because the individual’s belief in the cure triggers a physiological response. (10) Such is the power of the mind that...</t>
+          <t>...(0) where a patient experiences a real improvement in their condition after receiving a dummy treatment. This occurs (9) because the individual’s belief in the cure triggers a physiological response....</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>...a dummy treatment. This occurs (9) because the individual’s belief in the cure triggers a physiological response. (10) Such is the power of the mind that even sham surgeries have been known to alleviate symptoms. Researchers have found...</t>
+          <t>...because the individual’s belief in the cure triggers a physiological response. (10) Such is the power of the mind that even sham surgeries have been known to alleviate symptoms. Researchers have found...</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>...of the mind that even sham surgeries have been known to alleviate symptoms. Researchers have found that the effect is (11) far more complex than previously thought, involving neurochemical changes in the brain. (12) Although it was once...</t>
+          <t>...of the mind that even sham surgeries have been known to alleviate symptoms. Researchers have found that the effect is (11) far more complex than previously thought, involving neurochemical changes in the brain....</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>...found that the effect is (11) far more complex than previously thought, involving neurochemical changes in the brain. (12) Although it was once dismissed as a mere illusion, it is now considered an essential component of clinical trials....</t>
+          <t>...far more complex than previously thought, involving neurochemical changes in the brain. (12) Although it was once dismissed as a mere illusion, it is now considered an essential component of clinical trials....</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>...Although it was once dismissed as a mere illusion, it is now considered an essential component of clinical trials. (13) Not until scientists began using brain imaging did they truly understand how expectation modulates pain. (14) In spite...</t>
+          <t>...Although it was once dismissed as a mere illusion, it is now considered an essential component of clinical trials. (13) Not until scientists began using brain imaging did they truly understand how expectation modulates pain....</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>...trials. (13) Not until scientists began using brain imaging did they truly understand how expectation modulates pain. (14) In spite of the ethical dilemmas it presents, the use of placebos remains a standard practice in medical research....</t>
+          <t>...Not until scientists began using brain imaging did they truly understand how expectation modulates pain. (14) In spite of the ethical dilemmas it presents, the use of placebos remains a standard practice in medical research....</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -3221,33 +3223,33 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="60" customHeight="1">
+    <row r="23">
       <c r="A23" s="3" t="n">
         <v>22</v>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>...factor in Earth’s climate system, (0) referring to the proportion of solar energy reflected back into space. Surfaces (9) such as ice and snow have a high albedo, meaning they reflect most of the sunlight that hits them. (10) Conversely,...</t>
+          <t>...factor in Earth’s climate system, (0) referring to the proportion of solar energy reflected back into space. Surfaces (9) such as ice and snow have a high albedo, meaning they reflect most of the sunlight that hits them....</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>...space. Surfaces (9) such as ice and snow have a high albedo, meaning they reflect most of the sunlight that hits them. (10) Conversely, darker surfaces like the ocean or forests absorb more heat, leading to higher temperatures. (11) Although...</t>
+          <t>...such as ice and snow have a high albedo, meaning they reflect most of the sunlight that hits them. (10) Conversely, darker surfaces like the ocean or forests absorb more heat, leading to higher temperatures....</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>...them. (10) Conversely, darker surfaces like the ocean or forests absorb more heat, leading to higher temperatures. (11) Although this process occurs naturally, human activity is significantly altering the balance. As global temperatures...</t>
+          <t>...Conversely, darker surfaces like the ocean or forests absorb more heat, leading to higher temperatures. (11) Although this process occurs naturally, human activity is significantly altering the balance. As global temperatures...</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>...human activity is significantly altering the balance. As global temperatures rise, Arctic ice begins to melt, (12) which reduces the planet's overall reflectivity. (13) Not until the ice disappears do we fully realize how much heat...</t>
+          <t>...human activity is significantly altering the balance. As global temperatures rise, Arctic ice begins to melt, (12) which reduces the planet's overall reflectivity....</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>...balance. As global temperatures rise, Arctic ice begins to melt, (12) which reduces the planet's overall reflectivity. (13) Not until the ice disappears do we fully realize how much heat the open water absorbs, creating a dangerous feedback...</t>
+          <t>...which reduces the planet's overall reflectivity. (13) Not until the ice disappears do we fully realize how much heat the open water absorbs, creating a dangerous feedback...</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
@@ -3257,12 +3259,12 @@
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>...In spite of international efforts to curb emissions, the loss of reflective surfaces continues at an alarming rate. (15) Provided that we can preserve the remaining glaciers, we might slow down the warming process. (16) Whether or not the...</t>
+          <t>...In spite of international efforts to curb emissions, the loss of reflective surfaces continues at an alarming rate. (15) Provided that we can preserve the remaining glaciers, we might slow down the warming process....</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>...an alarming rate. (15) Provided that we can preserve the remaining glaciers, we might slow down the warming process. (16) Whether or not the Earth can recover from these changes remains an open question among climatologists today. This...</t>
+          <t>...Provided that we can preserve the remaining glaciers, we might slow down the warming process. (16) Whether or not the Earth can recover from these changes remains an open question among climatologists today. This...</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
@@ -3346,7 +3348,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="60" customHeight="1">
+    <row r="24">
       <c r="A24" s="2" t="n">
         <v>23</v>
       </c>
@@ -3357,37 +3359,37 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>...has advanced rapidly in urban centers, many rural areas still struggle with basic connectivity. This disparity is (10) not only a matter of convenience but also a significant barrier to education and economic opportunity. (11) Unless...</t>
+          <t>...has advanced rapidly in urban centers, many rural areas still struggle with basic connectivity. This disparity is (10) not only a matter of convenience but also a significant barrier to education and economic opportunity....</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>...is (10) not only a matter of convenience but also a significant barrier to education and economic opportunity. (11) Unless governments invest in infrastructure, millions of people will remain excluded from the modern economy....</t>
+          <t>...not only a matter of convenience but also a significant barrier to education and economic opportunity. (11) Unless governments invest in infrastructure, millions of people will remain excluded from the modern economy....</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>...in infrastructure, millions of people will remain excluded from the modern economy. Researchers have pointed out that (12) even in developed countries, low-income households often lack the devices necessary for remote work. (13) Not until...</t>
+          <t>...in infrastructure, millions of people will remain excluded from the modern economy. Researchers have pointed out that (12) even in developed countries, low-income households often lack the devices necessary for remote work....</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>...out that (12) even in developed countries, low-income households often lack the devices necessary for remote work. (13) Not until high-speed internet is treated as a public utility will this gap truly begin to close. (14) Despite the...</t>
+          <t>...even in developed countries, low-income households often lack the devices necessary for remote work. (13) Not until high-speed internet is treated as a public utility will this gap truly begin to close....</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>...for remote work. (13) Not until high-speed internet is treated as a public utility will this gap truly begin to close. (14) Despite the challenges, some non-profit organizations are working to provide affordable hardware to schools in need....</t>
+          <t>...Not until high-speed internet is treated as a public utility will this gap truly begin to close. (14) Despite the challenges, some non-profit organizations are working to provide affordable hardware to schools in need....</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>...Despite the challenges, some non-profit organizations are working to provide affordable hardware to schools in need. (15) Since the pandemic began, the urgency of this issue has become clearer than ever before. (16) Such is the importance...</t>
+          <t>...Despite the challenges, some non-profit organizations are working to provide affordable hardware to schools in need. (15) Since the pandemic began, the urgency of this issue has become clearer than ever before....</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>...to schools in need. (15) Since the pandemic began, the urgency of this issue has become clearer than ever before. (16) Such is the importance of digital literacy that it is now considered a fundamental skill for the twenty-first century....</t>
+          <t>...Since the pandemic began, the urgency of this issue has become clearer than ever before. (16) Such is the importance of digital literacy that it is now considered a fundamental skill for the twenty-first century....</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3471,28 +3473,28 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="60" customHeight="1">
+    <row r="25">
       <c r="A25" s="3" t="n">
         <v>24</v>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>...searching for planets orbiting stars (0) other than our own Sun, known as exoplanets. The first confirmed discovery (9) took place in the early 1990s, changing our perspective on the universe. (10) Since then, thousands of these distant...</t>
+          <t>...searching for planets orbiting stars (0) other than our own Sun, known as exoplanets. The first confirmed discovery (9) took place in the early 1990s, changing our perspective on the universe....</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>...exoplanets. The first confirmed discovery (9) took place in the early 1990s, changing our perspective on the universe. (10) Since then, thousands of these distant worlds have been identified using advanced telescopes. One common method...</t>
+          <t>...took place in the early 1990s, changing our perspective on the universe. (10) Since then, thousands of these distant worlds have been identified using advanced telescopes. One common method...</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>...identified using advanced telescopes. One common method involves monitoring a star for a slight dip in brightness, (11) which occurs when a planet passes in front of it. (12) Although most discovered exoplanets are gas giants, scientists...</t>
+          <t>...identified using advanced telescopes. One common method involves monitoring a star for a slight dip in brightness, (11) which occurs when a planet passes in front of it....</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>...involves monitoring a star for a slight dip in brightness, (11) which occurs when a planet passes in front of it. (12) Although most discovered exoplanets are gas giants, scientists are increasingly focused on finding Earth-like worlds....</t>
+          <t>...which occurs when a planet passes in front of it. (12) Although most discovered exoplanets are gas giants, scientists are increasingly focused on finding Earth-like worlds....</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
@@ -3502,12 +3504,12 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>...until recently have we possessed the technology to analyze the atmospheres of these far-off planets for signs of life. (14) Provided that a planet is located within the 'habitable zone', it could theoretically support liquid water. (15) In...</t>
+          <t>...until recently have we possessed the technology to analyze the atmospheres of these far-off planets for signs of life. (14) Provided that a planet is located within the 'habitable zone', it could theoretically support liquid water....</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>...life. (14) Provided that a planet is located within the 'habitable zone', it could theoretically support liquid water. (15) In spite of the vast distances involved, space agencies are planning future missions to study these candidates in more...</t>
+          <t>...Provided that a planet is located within the 'habitable zone', it could theoretically support liquid water. (15) In spite of the vast distances involved, space agencies are planning future missions to study these candidates in more...</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
@@ -3596,7 +3598,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="60" customHeight="1">
+    <row r="26">
       <c r="A26" s="2" t="n">
         <v>25</v>
       </c>
@@ -3607,12 +3609,12 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>...researchers have studied primate communication for decades, the gap between animal calls and human language is vast. (10) Such is the complexity of syntax that many linguists believe it required a unique genetic mutation. (11) Provided that...</t>
+          <t>...researchers have studied primate communication for decades, the gap between animal calls and human language is vast. (10) Such is the complexity of syntax that many linguists believe it required a unique genetic mutation....</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>...is vast. (10) Such is the complexity of syntax that many linguists believe it required a unique genetic mutation. (11) Provided that early humans lived in increasingly large social groups, the need for precise communication would have...</t>
+          <t>...Such is the complexity of syntax that many linguists believe it required a unique genetic mutation. (11) Provided that early humans lived in increasingly large social groups, the need for precise communication would have...</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -3622,17 +3624,17 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>...only did language allow for better coordination during hunts, but it also facilitated the sharing of abstract ideas. (13) Regardless of how it first emerged, language transformed our species into the dominant force on the planet. (14) Not...</t>
+          <t>...only did language allow for better coordination during hunts, but it also facilitated the sharing of abstract ideas. (13) Regardless of how it first emerged, language transformed our species into the dominant force on the planet....</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>...(13) Regardless of how it first emerged, language transformed our species into the dominant force on the planet. (14) Not until the invention of writing systems did human knowledge begin to accumulate at an exponential rate. (15)...</t>
+          <t>...Regardless of how it first emerged, language transformed our species into the dominant force on the planet. (14) Not until the invention of writing systems did human knowledge begin to accumulate at an exponential rate....</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>...(14) Not until the invention of writing systems did human knowledge begin to accumulate at an exponential rate. (15) Despite the diversity of the world's six thousand languages, they all share certain underlying structural principles....</t>
+          <t>...Not until the invention of writing systems did human knowledge begin to accumulate at an exponential rate. (15) Despite the diversity of the world's six thousand languages, they all share certain underlying structural principles....</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3721,7 +3723,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="60" customHeight="1">
+    <row r="27">
       <c r="A27" s="3" t="n">
         <v>26</v>
       </c>
@@ -3732,17 +3734,17 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>...In addition to using tools, these birds have been observed solving multi-step puzzles that would baffle some primates. (10) Such is their problem-solving skill that they can plan for future events, a trait once thought unique to humans. (11)...</t>
+          <t>...In addition to using tools, these birds have been observed solving multi-step puzzles that would baffle some primates. (10) Such is their problem-solving skill that they can plan for future events, a trait once thought unique to humans....</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>...(10) Such is their problem-solving skill that they can plan for future events, a trait once thought unique to humans. (11) Although their brains are small, the density of their neurons is incredibly high, allowing for complex thought. (12)...</t>
+          <t>...Such is their problem-solving skill that they can plan for future events, a trait once thought unique to humans. (11) Although their brains are small, the density of their neurons is incredibly high, allowing for complex thought....</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>...(11) Although their brains are small, the density of their neurons is incredibly high, allowing for complex thought. (12) Not until researchers began testing them in controlled environments did the full extent of their intelligence become...</t>
+          <t>...Although their brains are small, the density of their neurons is incredibly high, allowing for complex thought. (12) Not until researchers began testing them in controlled environments did the full extent of their intelligence become...</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
@@ -3752,17 +3754,17 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>...that they are given enough mental stimulation, captive crows show signs of boredom if left alone for too long. (14) Regardless of the species, members of the corvid family demonstrate a high degree of social learning. (15) Not only...</t>
+          <t>...that they are given enough mental stimulation, captive crows show signs of boredom if left alone for too long. (14) Regardless of the species, members of the corvid family demonstrate a high degree of social learning....</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>...too long. (14) Regardless of the species, members of the corvid family demonstrate a high degree of social learning. (15) Not only can they recognize individual human faces, but they also pass this information down to their offspring. (16)...</t>
+          <t>...Regardless of the species, members of the corvid family demonstrate a high degree of social learning. (15) Not only can they recognize individual human faces, but they also pass this information down to their offspring....</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>...(15) Not only can they recognize individual human faces, but they also pass this information down to their offspring. (16) Whether this intelligence evolved due to their social nature or their varied diet is a question that continues to...</t>
+          <t>...Not only can they recognize individual human faces, but they also pass this information down to their offspring. (16) Whether this intelligence evolved due to their social nature or their varied diet is a question that continues to...</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
@@ -3846,18 +3848,18 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="60" customHeight="1">
+    <row r="28">
       <c r="A28" s="2" t="n">
         <v>27</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>...trend that has transformed the way we live, (0) with more than half of the world's population now residing in cities. (9) While cities offer economic opportunities and cultural diversity, they also face immense logistical challenges. (10)...</t>
+          <t>...trend that has transformed the way we live, (0) with more than half of the world's population now residing in cities. (9) While cities offer economic opportunities and cultural diversity, they also face immense logistical challenges....</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>...(9) While cities offer economic opportunities and cultural diversity, they also face immense logistical challenges. (10) Such is the scale of modern megacities that providing basic services like water and transport requires constant...</t>
+          <t>...While cities offer economic opportunities and cultural diversity, they also face immense logistical challenges. (10) Such is the scale of modern megacities that providing basic services like water and transport requires constant...</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -3867,17 +3869,17 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>...urban planners prioritize sustainability, the environmental impact of these massive hubs will become unsustainable. (12) Not only do cities consume vast amounts of energy, but they also produce the majority of global waste. (13) Regardless...</t>
+          <t>...urban planners prioritize sustainability, the environmental impact of these massive hubs will become unsustainable. (12) Not only do cities consume vast amounts of energy, but they also produce the majority of global waste....</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>...(12) Not only do cities consume vast amounts of energy, but they also produce the majority of global waste. (13) Regardless of these drawbacks, people continue to migrate to urban centers in search of a better life. (14) Not until...</t>
+          <t>...Not only do cities consume vast amounts of energy, but they also produce the majority of global waste. (13) Regardless of these drawbacks, people continue to migrate to urban centers in search of a better life....</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>...waste. (13) Regardless of these drawbacks, people continue to migrate to urban centers in search of a better life. (14) Not until recently have architects begun to design 'green' buildings that incorporate vertical gardens to improve air...</t>
+          <t>...Regardless of these drawbacks, people continue to migrate to urban centers in search of a better life. (14) Not until recently have architects begun to design 'green' buildings that incorporate vertical gardens to improve air...</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -3971,7 +3973,7 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="60" customHeight="1">
+    <row r="29">
       <c r="A29" s="3" t="n">
         <v>28</v>
       </c>
@@ -3982,32 +3984,32 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>...when this breakthrough occurred remains a matter of debate, evidence suggests it happened over a million years ago. (10) Such was the impact of cooked food on the human diet that it led to significant changes in brain size. (11) Provided...</t>
+          <t>...when this breakthrough occurred remains a matter of debate, evidence suggests it happened over a million years ago. (10) Such was the impact of cooked food on the human diet that it led to significant changes in brain size....</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>...years ago. (10) Such was the impact of cooked food on the human diet that it led to significant changes in brain size. (11) Provided that early humans could maintain a constant flame, they were able to migrate into much colder climates. (12)...</t>
+          <t>...Such was the impact of cooked food on the human diet that it led to significant changes in brain size. (11) Provided that early humans could maintain a constant flame, they were able to migrate into much colder climates....</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>...(11) Provided that early humans could maintain a constant flame, they were able to migrate into much colder climates. (12) Not only did fire provide warmth and light, but it also served as a focal point for social interaction. (13)...</t>
+          <t>...Provided that early humans could maintain a constant flame, they were able to migrate into much colder climates. (12) Not only did fire provide warmth and light, but it also served as a focal point for social interaction....</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>...climates. (12) Not only did fire provide warmth and light, but it also served as a focal point for social interaction. (13) Regardless of the difficulties involved in starting a fire, it became an essential part of daily life for primitive...</t>
+          <t>...Not only did fire provide warmth and light, but it also served as a focal point for social interaction. (13) Regardless of the difficulties involved in starting a fire, it became an essential part of daily life for primitive...</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>...of the difficulties involved in starting a fire, it became an essential part of daily life for primitive tribes. (14) Not until fire was used to forge tools did the technological advancement of humanity truly begin to accelerate. (15)...</t>
+          <t>...of the difficulties involved in starting a fire, it became an essential part of daily life for primitive tribes. (14) Not until fire was used to forge tools did the technological advancement of humanity truly begin to accelerate....</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>...(14) Not until fire was used to forge tools did the technological advancement of humanity truly begin to accelerate. (15) Despite the risks associated with such a powerful force, it was harnessed to clear land for agriculture and eventually...</t>
+          <t>...Not until fire was used to forge tools did the technological advancement of humanity truly begin to accelerate. (15) Despite the risks associated with such a powerful force, it was harnessed to clear land for agriculture and eventually...</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
@@ -4096,7 +4098,7 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="60" customHeight="1">
+    <row r="30">
       <c r="A30" s="2" t="n">
         <v>29</v>
       </c>
@@ -4107,17 +4109,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>...(9) Although we often associate light with heat, this 'cold light' is remarkably efficient, losing very little energy. (10) Such is the darkness of the midnight zone that over ninety percent of creatures there have evolved some form of light....</t>
+          <t>...Although we often associate light with heat, this 'cold light' is remarkably efficient, losing very little energy. (10) Such is the darkness of the midnight zone that over ninety percent of creatures there have evolved some form of light....</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>...Such is the darkness of the midnight zone that over ninety percent of creatures there have evolved some form of light. (11) Provided that an organism can produce its own glow, it can use it to attract prey or communicate with mates. (12) Not...</t>
+          <t>...Such is the darkness of the midnight zone that over ninety percent of creatures there have evolved some form of light. (11) Provided that an organism can produce its own glow, it can use it to attract prey or communicate with mates....</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>...(11) Provided that an organism can produce its own glow, it can use it to attract prey or communicate with mates. (12) Not only do deep-sea fish use light for hunting, but they also employ it as a clever defense mechanism against...</t>
+          <t>...Provided that an organism can produce its own glow, it can use it to attract prey or communicate with mates. (12) Not only do deep-sea fish use light for hunting, but they also employ it as a clever defense mechanism against...</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -4221,7 +4223,7 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="60" customHeight="1">
+    <row r="31">
       <c r="A31" s="3" t="n">
         <v>30</v>
       </c>
@@ -4252,12 +4254,12 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>...of the concerns about job displacement, the integration of AI into the workforce appears to be an inevitable process. (14) Not until the advent of deep learning did machines begin to mimic human cognitive functions with such accuracy. (15)...</t>
+          <t>...of the concerns about job displacement, the integration of AI into the workforce appears to be an inevitable process. (14) Not until the advent of deep learning did machines begin to mimic human cognitive functions with such accuracy....</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>...(14) Not until the advent of deep learning did machines begin to mimic human cognitive functions with such accuracy. (15) Despite the challenges, many believe that AI will ultimately enhance human creativity rather than replace it entirely....</t>
+          <t>...Not until the advent of deep learning did machines begin to mimic human cognitive functions with such accuracy. (15) Despite the challenges, many believe that AI will ultimately enhance human creativity rather than replace it entirely....</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
@@ -4346,7 +4348,7 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="60" customHeight="1">
+    <row r="32">
       <c r="A32" s="2" t="n">
         <v>31</v>
       </c>
@@ -4362,17 +4364,17 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>...the sensitivity of coral to temperature that even a slight increase in ocean warmth can trigger widespread bleaching. (11) Provided that global carbon emissions are reduced, there is still hope for the reef to recover over time. (12) Not...</t>
+          <t>...the sensitivity of coral to temperature that even a slight increase in ocean warmth can trigger widespread bleaching. (11) Provided that global carbon emissions are reduced, there is still hope for the reef to recover over time....</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>...(11) Provided that global carbon emissions are reduced, there is still hope for the reef to recover over time. (12) Not only do these corals provide a habitat for marine life, but they also protect coastlines from erosion. (13)...</t>
+          <t>...Provided that global carbon emissions are reduced, there is still hope for the reef to recover over time. (12) Not only do these corals provide a habitat for marine life, but they also protect coastlines from erosion....</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>...time. (12) Not only do these corals provide a habitat for marine life, but they also protect coastlines from erosion. (13) Regardless of its immense size, the reef is a fragile structure that requires careful management and international...</t>
+          <t>...Not only do these corals provide a habitat for marine life, but they also protect coastlines from erosion. (13) Regardless of its immense size, the reef is a fragile structure that requires careful management and international...</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -4382,12 +4384,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>...did scientists fully understand the complex symbiotic relationship between the coral and the algae living within them. (15) In spite of the damage already done, restoration projects are working to cultivate heat-resistant coral strains. (16)...</t>
+          <t>...did scientists fully understand the complex symbiotic relationship between the coral and the algae living within them. (15) In spite of the damage already done, restoration projects are working to cultivate heat-resistant coral strains....</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>...(15) In spite of the damage already done, restoration projects are working to cultivate heat-resistant coral strains. (16) Whether these efforts will be enough to save this natural masterpiece remains a major concern for environmentalists....</t>
+          <t>...In spite of the damage already done, restoration projects are working to cultivate heat-resistant coral strains. (16) Whether these efforts will be enough to save this natural masterpiece remains a major concern for environmentalists....</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -4471,7 +4473,7 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="60" customHeight="1">
+    <row r="33">
       <c r="A33" s="3" t="n">
         <v>32</v>
       </c>
@@ -4482,17 +4484,17 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>...(9) Although it is often associated with athletes and musicians, anyone can experience flow during a challenging task. (10) Such is the intensity of this focus that people often report feeling a sense of effortless control over their actions....</t>
+          <t>...Although it is often associated with athletes and musicians, anyone can experience flow during a challenging task. (10) Such is the intensity of this focus that people often report feeling a sense of effortless control over their actions....</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>...Such is the intensity of this focus that people often report feeling a sense of effortless control over their actions. (11) Provided that the difficulty of the task matches the individual's skill level, the conditions for flow are ideal. (12)...</t>
+          <t>...Such is the intensity of this focus that people often report feeling a sense of effortless control over their actions. (11) Provided that the difficulty of the task matches the individual's skill level, the conditions for flow are ideal....</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>...(11) Provided that the difficulty of the task matches the individual's skill level, the conditions for flow are ideal. (12) Not only does this state increase productivity, but it also significantly enhances a person's overall sense of...</t>
+          <t>...Provided that the difficulty of the task matches the individual's skill level, the conditions for flow are ideal. (12) Not only does this state increase productivity, but it also significantly enhances a person's overall sense of...</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
@@ -4596,7 +4598,7 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="60" customHeight="1">
+    <row r="34">
       <c r="A34" s="2" t="n">
         <v>33</v>
       </c>
@@ -4627,12 +4629,12 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>...Regardless of the political changes in the regions it crossed, the demand for exotic products kept the routes active. (14) Not until the rise of maritime trade did the land-based Silk Road begin to lose its primary significance. (15) Despite...</t>
+          <t>...Regardless of the political changes in the regions it crossed, the demand for exotic products kept the routes active. (14) Not until the rise of maritime trade did the land-based Silk Road begin to lose its primary significance....</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>...active. (14) Not until the rise of maritime trade did the land-based Silk Road begin to lose its primary significance. (15) Despite its eventual decline, its legacy remains a testament to the enduring human desire for connection and...</t>
+          <t>...Not until the rise of maritime trade did the land-based Silk Road begin to lose its primary significance. (15) Despite its eventual decline, its legacy remains a testament to the enduring human desire for connection and...</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -4721,7 +4723,7 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="60" customHeight="1">
+    <row r="35">
       <c r="A35" s="3" t="n">
         <v>34</v>
       </c>
@@ -4846,7 +4848,7 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="60" customHeight="1">
+    <row r="36">
       <c r="A36" s="2" t="n">
         <v>35</v>
       </c>
@@ -4857,12 +4859,12 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>...the movements may look random to a human observer, they provide precise coordinates to other members of the hive. (10) Such is the accuracy of this dance that it can convey both the distance and the direction of a nectar source. (11)...</t>
+          <t>...the movements may look random to a human observer, they provide precise coordinates to other members of the hive. (10) Such is the accuracy of this dance that it can convey both the distance and the direction of a nectar source....</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>...(10) Such is the accuracy of this dance that it can convey both the distance and the direction of a nectar source. (11) Provided that the sun is visible, the bees use its position as a reference point for their complex aerial...</t>
+          <t>...Such is the accuracy of this dance that it can convey both the distance and the direction of a nectar source. (11) Provided that the sun is visible, the bees use its position as a reference point for their complex aerial...</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -4971,7 +4973,7 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="60" customHeight="1">
+    <row r="37">
       <c r="A37" s="3" t="n">
         <v>36</v>
       </c>
@@ -5096,7 +5098,7 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="60" customHeight="1">
+    <row r="38">
       <c r="A38" s="2" t="n">
         <v>37</v>
       </c>
@@ -5107,12 +5109,12 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>...fraught with danger from predators and treacherous river crossings, the animals must move to find fresh grazing lands. (10) Such is the scale of this movement that it can be tracked by satellites orbiting high above the Earth. (11) Provided...</t>
+          <t>...fraught with danger from predators and treacherous river crossings, the animals must move to find fresh grazing lands. (10) Such is the scale of this movement that it can be tracked by satellites orbiting high above the Earth....</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>...lands. (10) Such is the scale of this movement that it can be tracked by satellites orbiting high above the Earth. (11) Provided that the seasonal rains arrive on time, the vast herds follow a predictable clockwise route through the...</t>
+          <t>...Such is the scale of this movement that it can be tracked by satellites orbiting high above the Earth. (11) Provided that the seasonal rains arrive on time, the vast herds follow a predictable clockwise route through the...</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -5221,7 +5223,7 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="60" customHeight="1">
+    <row r="39">
       <c r="A39" s="3" t="n">
         <v>38</v>
       </c>
@@ -5237,12 +5239,12 @@
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>...the significance of this observation that it eventually led to the development of the world’s first true antibiotic. (11) Provided that a patient was treated early enough, infections that were once fatal could now be cured with ease. (12)...</t>
+          <t>...the significance of this observation that it eventually led to the development of the world’s first true antibiotic. (11) Provided that a patient was treated early enough, infections that were once fatal could now be cured with ease....</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>...(11) Provided that a patient was treated early enough, infections that were once fatal could now be cured with ease. (12) Not only did penicillin save countless lives during World War II, but it also opened the door to modern pharmaceutical...</t>
+          <t>...Provided that a patient was treated early enough, infections that were once fatal could now be cured with ease. (12) Not only did penicillin save countless lives during World War II, but it also opened the door to modern pharmaceutical...</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
@@ -5346,7 +5348,7 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="60" customHeight="1">
+    <row r="40">
       <c r="A40" s="2" t="n">
         <v>39</v>
       </c>
@@ -5367,22 +5369,22 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>...individual focuses on what truly adds value to their life, the process of decluttering can be incredibly liberating. (12) Not only does minimalism reduce financial stress, but it also allows for greater mental clarity and focus. (13)...</t>
+          <t>...individual focuses on what truly adds value to their life, the process of decluttering can be incredibly liberating. (12) Not only does minimalism reduce financial stress, but it also allows for greater mental clarity and focus....</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>...(12) Not only does minimalism reduce financial stress, but it also allows for greater mental clarity and focus. (13) Regardless of the size of one’s home, the practice of intentional living can be applied to any environment. (14) Not...</t>
+          <t>...Not only does minimalism reduce financial stress, but it also allows for greater mental clarity and focus. (13) Regardless of the size of one’s home, the practice of intentional living can be applied to any environment....</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>...(13) Regardless of the size of one’s home, the practice of intentional living can be applied to any environment. (14) Not until people start letting go of physical items do they realize how much emotional weight they were carrying. (15)...</t>
+          <t>...Regardless of the size of one’s home, the practice of intentional living can be applied to any environment. (14) Not until people start letting go of physical items do they realize how much emotional weight they were carrying....</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>...(14) Not until people start letting go of physical items do they realize how much emotional weight they were carrying. (15) Despite the initial difficulty of breaking old habits, many find that a simpler life is far more rewarding than they...</t>
+          <t>...Not until people start letting go of physical items do they realize how much emotional weight they were carrying. (15) Despite the initial difficulty of breaking old habits, many find that a simpler life is far more rewarding than they...</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
@@ -5471,7 +5473,7 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="60" customHeight="1">
+    <row r="41">
       <c r="A41" s="3" t="n">
         <v>40</v>
       </c>
@@ -5497,12 +5499,12 @@
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>...did the mammoths face a changing environment, but they also suffered from a significant loss of genetic diversity. (13) Regardless of the specific cause, their final disappearance marked the end of an era for Earth's megafauna. (14) Not...</t>
+          <t>...did the mammoths face a changing environment, but they also suffered from a significant loss of genetic diversity. (13) Regardless of the specific cause, their final disappearance marked the end of an era for Earth's megafauna....</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>...(13) Regardless of the specific cause, their final disappearance marked the end of an era for Earth's megafauna. (14) Not until recently have scientists successfully sequenced the mammoth's entire genome from well-preserved remains...</t>
+          <t>...Regardless of the specific cause, their final disappearance marked the end of an era for Earth's megafauna. (14) Not until recently have scientists successfully sequenced the mammoth's entire genome from well-preserved remains...</t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
@@ -5596,7 +5598,7 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="60" customHeight="1">
+    <row r="42">
       <c r="A42" s="2" t="n">
         <v>41</v>
       </c>
@@ -5721,7 +5723,7 @@
         </is>
       </c>
     </row>
-    <row r="43" ht="60" customHeight="1">
+    <row r="43">
       <c r="A43" s="3" t="n">
         <v>42</v>
       </c>
@@ -5732,12 +5734,12 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>...remains one of the most hostile environments on Earth, recent expeditions have found life thriving in its dark depths. (10) Such is the extreme pressure at the bottom that it would crush a regular submarine in a matter of seconds. (11)...</t>
+          <t>...remains one of the most hostile environments on Earth, recent expeditions have found life thriving in its dark depths. (10) Such is the extreme pressure at the bottom that it would crush a regular submarine in a matter of seconds....</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>...(10) Such is the extreme pressure at the bottom that it would crush a regular submarine in a matter of seconds. (11) Provided that specialized equipment is used, humans can safely descend to explore this vast, uncharted territory of...</t>
+          <t>...Such is the extreme pressure at the bottom that it would crush a regular submarine in a matter of seconds. (11) Provided that specialized equipment is used, humans can safely descend to explore this vast, uncharted territory of...</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
@@ -5752,12 +5754,12 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>...the darkness, these organisms have adapted to survive using chemosynthesis instead of the more common photosynthesis. (14) Not until the historic dive of the Trieste in 1960 did we have any real understanding of what lay at the bottom. (15)...</t>
+          <t>...the darkness, these organisms have adapted to survive using chemosynthesis instead of the more common photosynthesis. (14) Not until the historic dive of the Trieste in 1960 did we have any real understanding of what lay at the bottom....</t>
         </is>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t>...(14) Not until the historic dive of the Trieste in 1960 did we have any real understanding of what lay at the bottom. (15) In spite of the incredible depth, traces of plastic pollution have unfortunately been discovered even in these remote...</t>
+          <t>...Not until the historic dive of the Trieste in 1960 did we have any real understanding of what lay at the bottom. (15) In spite of the incredible depth, traces of plastic pollution have unfortunately been discovered even in these remote...</t>
         </is>
       </c>
       <c r="I43" s="3" t="inlineStr">
@@ -5846,7 +5848,7 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="60" customHeight="1">
+    <row r="44">
       <c r="A44" s="2" t="n">
         <v>43</v>
       </c>
@@ -5872,12 +5874,12 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>...did this technique change painting, but it also influenced architecture and urban planning during the Renaissance. (13) Regardless of the subject matter, the use of perspective gave works a newfound authority and intellectual depth. (14)...</t>
+          <t>...did this technique change painting, but it also influenced architecture and urban planning during the Renaissance. (13) Regardless of the subject matter, the use of perspective gave works a newfound authority and intellectual depth....</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>...(13) Regardless of the subject matter, the use of perspective gave works a newfound authority and intellectual depth. (14) Not until the early 1900s did modern movements like Cubism begin to deliberately reject these traditional rules of...</t>
+          <t>...Regardless of the subject matter, the use of perspective gave works a newfound authority and intellectual depth. (14) Not until the early 1900s did modern movements like Cubism begin to deliberately reject these traditional rules of...</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -5971,7 +5973,7 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="60" customHeight="1">
+    <row r="45">
       <c r="A45" s="3" t="n">
         <v>44</v>
       </c>
@@ -5982,22 +5984,22 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>...Although today we consume it mostly as a sweet treat, for the Mayans and Aztecs, it was primarily a bitter beverage. (10) Such was the value of cacao beans that they were even used as a form of currency in trade. (11) Provided that a person...</t>
+          <t>...Although today we consume it mostly as a sweet treat, for the Mayans and Aztecs, it was primarily a bitter beverage. (10) Such was the value of cacao beans that they were even used as a form of currency in trade....</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>...a bitter beverage. (10) Such was the value of cacao beans that they were even used as a form of currency in trade. (11) Provided that a person was of high social status, they could enjoy this 'drink of the gods' during sacred rituals....</t>
+          <t>...Such was the value of cacao beans that they were even used as a form of currency in trade. (11) Provided that a person was of high social status, they could enjoy this 'drink of the gods' during sacred rituals....</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>...Provided that a person was of high social status, they could enjoy this 'drink of the gods' during sacred rituals. (12) Not only was cacao important for its taste, but it was also believed to possess significant medicinal properties. (13)...</t>
+          <t>...Provided that a person was of high social status, they could enjoy this 'drink of the gods' during sacred rituals. (12) Not only was cacao important for its taste, but it was also believed to possess significant medicinal properties....</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>...(12) Not only was cacao important for its taste, but it was also believed to possess significant medicinal properties. (13) Regardless of the long journey across the Atlantic, chocolate quickly became a luxury item in the royal courts of...</t>
+          <t>...Not only was cacao important for its taste, but it was also believed to possess significant medicinal properties. (13) Regardless of the long journey across the Atlantic, chocolate quickly became a luxury item in the royal courts of...</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
@@ -6096,7 +6098,7 @@
         </is>
       </c>
     </row>
-    <row r="46" ht="60" customHeight="1">
+    <row r="46">
       <c r="A46" s="2" t="n">
         <v>45</v>
       </c>
@@ -6112,12 +6114,12 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>...is the difficulty of mimicking human conversation that very few programs have come close to passing it convincingly. (11) Provided that a computer can deceive a human judge into thinking it is also human, it is said to have passed. (12) Not...</t>
+          <t>...is the difficulty of mimicking human conversation that very few programs have come close to passing it convincingly. (11) Provided that a computer can deceive a human judge into thinking it is also human, it is said to have passed....</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>...(11) Provided that a computer can deceive a human judge into thinking it is also human, it is said to have passed. (12) Not only did Turing's work provide a philosophical framework for AI, but it also anticipated the future challenges of...</t>
+          <t>...Provided that a computer can deceive a human judge into thinking it is also human, it is said to have passed. (12) Not only did Turing's work provide a philosophical framework for AI, but it also anticipated the future challenges of...</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -6221,7 +6223,7 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="60" customHeight="1">
+    <row r="47">
       <c r="A47" s="3" t="n">
         <v>46</v>
       </c>
@@ -6346,7 +6348,7 @@
         </is>
       </c>
     </row>
-    <row r="48" ht="60" customHeight="1">
+    <row r="48">
       <c r="A48" s="2" t="n">
         <v>47</v>
       </c>
@@ -6471,7 +6473,7 @@
         </is>
       </c>
     </row>
-    <row r="49" ht="60" customHeight="1">
+    <row r="49">
       <c r="A49" s="3" t="n">
         <v>48</v>
       </c>
@@ -6482,17 +6484,17 @@
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>...had existed for centuries, they were previously handwritten and extremely expensive for the average person to own. (10) Such was the efficiency of the new press that it allowed for the mass production of texts at an affordable cost. (11)...</t>
+          <t>...had existed for centuries, they were previously handwritten and extremely expensive for the average person to own. (10) Such was the efficiency of the new press that it allowed for the mass production of texts at an affordable cost....</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>...(10) Such was the efficiency of the new press that it allowed for the mass production of texts at an affordable cost. (11) Provided that a person could read, they suddenly had access to a vast world of knowledge and information. (12) Not...</t>
+          <t>...Such was the efficiency of the new press that it allowed for the mass production of texts at an affordable cost. (11) Provided that a person could read, they suddenly had access to a vast world of knowledge and information....</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>...cost. (11) Provided that a person could read, they suddenly had access to a vast world of knowledge and information. (12) Not only did the printing press facilitate the spread of religious ideas, but it also laid the foundation for the...</t>
+          <t>...Provided that a person could read, they suddenly had access to a vast world of knowledge and information. (12) Not only did the printing press facilitate the spread of religious ideas, but it also laid the foundation for the...</t>
         </is>
       </c>
       <c r="F49" s="3" t="inlineStr">
@@ -6596,7 +6598,7 @@
         </is>
       </c>
     </row>
-    <row r="50" ht="60" customHeight="1">
+    <row r="50">
       <c r="A50" s="2" t="n">
         <v>49</v>
       </c>
@@ -6607,17 +6609,17 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>...had existed for centuries, they were previously handwritten and extremely expensive for the average person to own. (10) Such was the efficiency of the new press that it allowed for the mass production of texts at an affordable cost. (11)...</t>
+          <t>...had existed for centuries, they were previously handwritten and extremely expensive for the average person to own. (10) Such was the efficiency of the new press that it allowed for the mass production of texts at an affordable cost....</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>...(10) Such was the efficiency of the new press that it allowed for the mass production of texts at an affordable cost. (11) Provided that a person could read, they suddenly had access to a vast world of knowledge and information. (12) Not...</t>
+          <t>...Such was the efficiency of the new press that it allowed for the mass production of texts at an affordable cost. (11) Provided that a person could read, they suddenly had access to a vast world of knowledge and information....</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>...cost. (11) Provided that a person could read, they suddenly had access to a vast world of knowledge and information. (12) Not only did the printing press facilitate the spread of religious ideas, but it also laid the foundation for the...</t>
+          <t>...Provided that a person could read, they suddenly had access to a vast world of knowledge and information. (12) Not only did the printing press facilitate the spread of religious ideas, but it also laid the foundation for the...</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -6721,7 +6723,7 @@
         </is>
       </c>
     </row>
-    <row r="51" ht="60" customHeight="1">
+    <row r="51">
       <c r="A51" s="3" t="n">
         <v>50</v>
       </c>
